--- a/output/ldf-alignment-data-required.xlsx
+++ b/output/ldf-alignment-data-required.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data Required'!$A$1:$M$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data Required'!$A$1:$M$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -70,7 +70,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CDD2B7"/>
+        <fgColor rgb="00F3E9D2"/>
       </patternFill>
     </fill>
     <fill>
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -626,12 +626,12 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Leadership Levels poster: OCDT (Lead Self) to Junior Officer (Lead Teams). Poster states rank alignment is 'only an estimation'.</t>
+          <t>Meeting 9 Sep: OCDT to 2LT (commissioning on NZCC).</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>TO CONFIRM</t>
+          <t>STATED 9 SEP</t>
         </is>
       </c>
       <c r="K2" s="4" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>LDS poster: LDS Lead Teams course embedded in single-Service development courses.</t>
+          <t>Meeting 9 Sep: NZCC includes ELDA Lead Teams (the former Nemesis, rebranded with the same learning outcomes) and LDS Lead Teams, delivered by ALC at OCS in March, two years running.</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>TO CONFIRM</t>
+          <t>STATED 9 SEP</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr"/>
@@ -734,10 +734,14 @@
           <t>SOLO prerequisites; promotion course CDS; Army promotion policy</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr">
-        <is>
-          <t>DATA REQUIRED</t>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Meeting 9 Sep: Embedded: qualifying on NZCC qualifies both LDS and ELDA Lead Teams.</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>STATED 9 SEP</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr"/>
@@ -787,12 +791,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Leadership Levels poster: PTE to LCPL / CPL. 'Only an estimation'.</t>
+          <t>Meeting 9 Sep: PTE to LCPL (JNCO course).</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>TO CONFIRM</t>
+          <t>STATED 9 SEP</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr"/>
@@ -842,12 +846,12 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>LDS poster: LDS Lead Teams course embedded in single-Service development courses. Session documents: ELDA Lead Teams (A18011) is an included course within A1530 JNCO Course; D03020 LDS Lead Teams sequencing referenced.</t>
+          <t>Meeting 9 Sep: ELDA Lead Teams (A18011) embedded in the JNCO course (A1530) as the performance-under-pressure module; LDS Lead Teams (D03020) sequenced alongside.</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>TO CONFIRM</t>
+          <t>STATED 9 SEP</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr"/>
@@ -897,12 +901,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Session documents: ELDA Lead Teams is an included course within the A1530 JNCO Course.</t>
+          <t>Meeting 9 Sep: Mandated for PTE to LCPL as an included course within the JNCO course.</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>TO CONFIRM</t>
+          <t>STATED 9 SEP</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr"/>
@@ -952,12 +956,12 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Leadership Levels poster: Junior Officer spans Transition One and Two.</t>
+          <t>Meeting 9 Sep: 2LT and LT to CAPT; the substantive CAPT request.</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>TO CONFIRM</t>
+          <t>STATED 9 SEP</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr"/>
@@ -1007,12 +1011,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>LDS poster: LDS Lead Leaders course delivered by single-Service learning providers. Session documents: ELDA Lead Leaders (A18008) targets 2LT and LT; prerequisite D03030 / D03003 LDS Lead Leaders referenced.</t>
+          <t>Meeting 9 Sep: ELDA Lead Leaders (A18008) and LDS Lead Leaders, distributed and self-scheduled. Session documents: A18008 targets 2LT and LT; prerequisite D03030 / D03003 referenced.</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>TO CONFIRM</t>
+          <t>STATED 9 SEP</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr"/>
@@ -1062,12 +1066,12 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>The trigger for the tasking: a request to link Lead Leaders to promotion to substantive Captain, implying no current mandate. The single most important cell.</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>DATA REQUIRED</t>
+          <t>Meeting 9 Sep: Recommended, not mandated in promotion policy. Policed in function by OCS and COs: no 2LT or LT promotes to CAPT without it in practice. The single most important cell: confirm against promotion policy.</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>STATED 9 SEP</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr"/>
@@ -1117,12 +1121,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Leadership Levels poster: SGT / SSGT / WO band.</t>
+          <t>Meeting 9 Sep: CPL to SGT (SNCO course).</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>TO CONFIRM</t>
+          <t>STATED 9 SEP</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr"/>
@@ -1172,12 +1176,12 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>LDS poster: as for Officer. Session documents: ELDA Lead Leaders targets NCOs accepted onto A1531 SNCO Promotion Course.</t>
+          <t>Meeting 9 Sep: SNCO course (A1531) carries ELDA Lead Leaders (A18008) and LDS Lead Leaders (D03030).</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>TO CONFIRM</t>
+          <t>STATED 9 SEP</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr"/>
@@ -1227,12 +1231,12 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Session documents: D03030 LDS Lead Leaders listed as a prerequisite; ELDA Lead Leaders targets NCOs accepted onto A1531.</t>
+          <t>Meeting 9 Sep: Mandated in promotion policy: CPL promoting to SGT must complete the SNCO course, which carries it. 'Very clear on the NCO front.'</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>TO CONFIRM</t>
+          <t>STATED 9 SEP</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr"/>
@@ -1282,12 +1286,12 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Leadership Levels poster: MAJ (Transition Three).</t>
+          <t>Meeting 9 Sep: CAPT to MAJ; CAPT to OC is the largest jump in scope of influence.</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>TO CONFIRM</t>
+          <t>STATED 9 SEP</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr"/>
@@ -1337,12 +1341,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>LDS poster: LDS Lead Systems course delivered by ILD. Session documents: ELDA Lead Systems (A18010) targets Captains preparing for promotion to Major; A1302 Staff and Tactics Grade Two referenced.</t>
+          <t>Meeting 9 Sep: ELDA Lead Systems (A18010, ALC) and LDS Lead Systems (ILD). Session documents: A18010 targets CAPT preparing for MAJ; A1302 referenced.</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>TO CONFIRM</t>
+          <t>STATED 9 SEP</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr"/>
@@ -1390,10 +1394,14 @@
           <t>SOLO prerequisites; promotion course CDS; Army promotion policy</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr">
-        <is>
-          <t>DATA REQUIRED</t>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Meeting 9 Sep: Neither ELDA Lead Systems nor ILD LDS Lead Systems is mandated; neither is policed in function; uptake self-selecting. Confirm against promotion policy.</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>STATED 9 SEP</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr"/>
@@ -1443,12 +1451,12 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Leadership Levels poster: WO band; Tier 5 WO at Transition Four.</t>
+          <t>Meeting 9 Sep: SSGT to WO2; WO2 is the Lead Systems tick.</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>TO CONFIRM</t>
+          <t>STATED 9 SEP</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr"/>
@@ -1498,12 +1506,12 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>LDS poster: as for Officer. Session documents: ELDA Lead Systems targets SNCOs and WOs accepted onto A1532 WO Course.</t>
+          <t>Meeting 9 Sep: ELDA Lead Systems (A18010) on the WO course (A1532); LDS Lead Systems delivered by ILD, routinely before or after the promotion course because Army cannot guarantee a seat.</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>TO CONFIRM</t>
+          <t>STATED 9 SEP</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr"/>
@@ -1551,10 +1559,14 @@
           <t>SOLO prerequisites; promotion course CDS; Army promotion policy</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="5" t="inlineStr">
-        <is>
-          <t>DATA REQUIRED</t>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Meeting 9 Sep: ELDA Lead Systems mandated on the WO course. Whether ILD LDS Lead Systems is a prerequisite for WO2: understanding is yes, with a question mark. Dave to check the promotion-course CDS.</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>STATED 9 SEP</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr"/>
@@ -1604,12 +1616,12 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Leadership Levels poster: LTCOL (Transition Four).</t>
+          <t>Meeting 9 Sep: MAJ to LTCOL.</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>TO CONFIRM</t>
+          <t>STATED 9 SEP</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr"/>
@@ -1659,12 +1671,12 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>LDS poster: LDS Lead Capability course delivered by ILD.</t>
+          <t>Meeting 9 Sep: LDS Lead Capability, ILD tri-service course.</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>TO CONFIRM</t>
+          <t>STATED 9 SEP</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr"/>
@@ -1712,10 +1724,14 @@
           <t>SOLO prerequisites; promotion course CDS; Army promotion policy</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr">
-        <is>
-          <t>DATA REQUIRED</t>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Meeting 9 Sep: Not mandated; impression is that all MAJ to LTCOL complete it. Confirm against promotion policy.</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>STATED 9 SEP</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr"/>
@@ -1765,12 +1781,12 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Leadership Levels poster: Tier 5 WO.</t>
+          <t>Meeting 9 Sep: WO2 to WO1; WO1 is the Lead Capability tick.</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>TO CONFIRM</t>
+          <t>STATED 9 SEP</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr"/>
@@ -1820,12 +1836,12 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>LDS poster: LDS Lead Capability course delivered by ILD.</t>
+          <t>Meeting 9 Sep: LDS Lead Capability, ILD tri-service course.</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>TO CONFIRM</t>
+          <t>STATED 9 SEP</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr"/>
@@ -1873,10 +1889,14 @@
           <t>SOLO prerequisites; promotion course CDS; Army promotion policy</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>DATA REQUIRED</t>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Meeting 9 Sep: Expected for promotion to WO1; 'pretty sure' not mandated in policy; most attend subject to an ILD seat. Confirm against promotion policy.</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>STATED 9 SEP</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr"/>
@@ -1926,12 +1946,12 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Leadership Levels poster: COL (Transition Five).</t>
+          <t>Meeting 9 Sep: LTCOL and COL attend Lead Integrated Capability; senior MAJ do not.</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>TO CONFIRM</t>
+          <t>STATED 9 SEP</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr"/>
@@ -1981,12 +2001,12 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>LDS poster: LDS Lead Integrated course delivered by ILD.</t>
+          <t>Meeting 9 Sep: LDS Lead Integrated Capability: one ELDA week (ALC caving or Navy sailing as activity contractors) plus one LDS week in Wellington; ILD runs, facilitates and funds both. 12 to 16 students; ALC now runs one caving week a year.</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>TO CONFIRM</t>
+          <t>STATED 9 SEP</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr"/>
@@ -2034,10 +2054,14 @@
           <t>SOLO prerequisites; promotion course CDS; Army promotion policy</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr">
-        <is>
-          <t>DATA REQUIRED</t>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Meeting 9 Sep: Mandate not stated; attendance without exception (selected, scrutinised, ambitious).</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>STATED 9 SEP</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr"/>
@@ -2087,12 +2111,12 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Leadership Levels poster: Tier 4 WO.</t>
+          <t>Meeting 9 Sep: WO1s attend Lead Integrated Capability alongside LTCOL and COL.</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>TO CONFIRM</t>
+          <t>STATED 9 SEP</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr"/>
@@ -2142,12 +2166,12 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>LDS poster: LDS Lead Integrated course delivered by ILD.</t>
+          <t>Meeting 9 Sep: As for Officer.</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>TO CONFIRM</t>
+          <t>STATED 9 SEP</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr"/>
@@ -2195,10 +2219,14 @@
           <t>SOLO prerequisites; promotion course CDS; Army promotion policy</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="5" t="inlineStr">
-        <is>
-          <t>DATA REQUIRED</t>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Meeting 9 Sep: Mandate not stated; attendance without exception.</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>STATED 9 SEP</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr"/>
@@ -2248,12 +2276,12 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Leadership Levels poster: BRIG and above (Transition Six).</t>
+          <t>Meeting 9 Sep: COL and BRIG considered for the senior appointments.</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>TO CONFIRM</t>
+          <t>STATED 9 SEP</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr"/>
@@ -2303,12 +2331,12 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>LDS poster: LDS Lead Organisation course delivered by ILD.</t>
+          <t>Meeting 9 Sep: LDS Lead Organisation with an ELDA component (retreat setting, equine behaviour, psychometric profiling, external facilitation such as Rob Holt). Timing of the LDS element to check.</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>TO CONFIRM</t>
+          <t>STATED 9 SEP</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr"/>
@@ -2356,10 +2384,14 @@
           <t>SOLO prerequisites; promotion course CDS; Army promotion policy</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="5" t="inlineStr">
-        <is>
-          <t>DATA REQUIRED</t>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Meeting 9 Sep: Mandate not stated; all complete it well before required.</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>STATED 9 SEP</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr"/>
@@ -2409,12 +2441,12 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Leadership Levels poster: Tier 3 WO and above.</t>
+          <t>Meeting 9 Sep: Senior WO1s considered for the senior appointments (SMA level).</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>TO CONFIRM</t>
+          <t>STATED 9 SEP</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr"/>
@@ -2464,12 +2496,12 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>LDS poster: LDS Lead Organisation course delivered by ILD.</t>
+          <t>Meeting 9 Sep: As for Officer.</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>TO CONFIRM</t>
+          <t>STATED 9 SEP</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr"/>
@@ -2517,10 +2549,14 @@
           <t>SOLO prerequisites; promotion course CDS; Army promotion policy</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="5" t="inlineStr">
-        <is>
-          <t>DATA REQUIRED</t>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Meeting 9 Sep: Mandate not stated; all complete it well before required.</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>STATED 9 SEP</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr"/>
@@ -2552,7 +2588,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Army promotion policy: the authoritative statement of promotion prerequisites for each rank, Officer and Soldier.</t>
+          <t>Army promotion policy: the authoritative statement of promotion prerequisites for each rank, Officer and Soldier. The meeting's officer statements (T2 to T4) are checked here first.</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2638,7 +2674,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>ILD delivery data for Lead Capability and above: which Army ranks attend, when, and whether attendance is mandated.</t>
+          <t>ILD delivery data for Lead Systems and above: which Army ranks attend, when relative to the promotion course, seats available to Army, and whether attendance is mandated.</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2681,7 +2717,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>The authoritative Army view of which rank corresponds to each LDF transition, replacing the LDS poster estimate.</t>
+          <t>The authoritative Army view of which rank corresponds to each LDF transition. Meeting 9 Sep: WO2 is the Lead Systems tick, WO1 the Lead Capability tick; LIC attended by LTCOL, COL and WO1; Lead Org by COL, BRIG and senior WO1.</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2690,9 +2726,9 @@
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="5" t="inlineStr">
-        <is>
-          <t>DATA REQUIRED</t>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>STATED 9 SEP</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr"/>
@@ -2742,11 +2778,140 @@
       <c r="L42" s="4" t="inlineStr"/>
       <c r="M42" s="4" t="inlineStr"/>
     </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>X6</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr"/>
+      <c r="D43" s="2" t="inlineStr"/>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>History</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>The officer mandate history. Meeting 9 Sep: two-year pilot attaching Lead Leaders to Grade 2 and 3 coursing withdrawn as untenable time away from units; distributed self-scheduled approach agreed; Post Commissioning Programme delivered Lead Leaders before unit experience; AITC agreed in principle, then parked in a headquarters restructure; ACS not at the table for later redesigns. Dates and the AITC record to confirm.</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>AITC minutes; ACS records</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>STATED 9 SEP</t>
+        </is>
+      </c>
+      <c r="K43" s="4" t="inlineStr"/>
+      <c r="L43" s="4" t="inlineStr"/>
+      <c r="M43" s="4" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>X7</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr"/>
+      <c r="D44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Delivery</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>The 2012 division of delivery: single-Service providers to Lead Leaders, ILD for Lead Systems and above, Army retaining the ELDA function. Meeting 9 Sep: as stated; source document to cite.</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>ILD; NZDF leadership governance</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>STATED 9 SEP</t>
+        </is>
+      </c>
+      <c r="K44" s="4" t="inlineStr"/>
+      <c r="L44" s="4" t="inlineStr"/>
+      <c r="M44" s="4" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>X8</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr"/>
+      <c r="D45" s="2" t="inlineStr"/>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Explanation</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>The candidate explanation for the difference. Meeting 9 Sep: 'a scheduling oversight in the face of tempo'; non-required training is bumped; senior leaders assume the training is universal. Test against X1, X5 and X6 before it is presented as more than a candidate.</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>COMDT ACS; AITC</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>STATED 9 SEP</t>
+        </is>
+      </c>
+      <c r="K45" s="4" t="inlineStr"/>
+      <c r="L45" s="4" t="inlineStr"/>
+      <c r="M45" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M42"/>
+  <autoFilter ref="A1:M45"/>
   <dataValidations count="1">
-    <dataValidation sqref="J2:J42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"DATA REQUIRED,TO CONFIRM,KNOWN,NOT APPLICABLE"</formula1>
+    <dataValidation sqref="J2:J45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"DATA REQUIRED,TO CONFIRM,STATED 9 SEP,KNOWN,NOT APPLICABLE"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2759,7 +2924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A18"/>
+  <dimension ref="A1:A20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -2778,7 +2943,7 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>One row per transition (T1 to T6), per continuum (Officer, Soldier), per fact (promotion point, development intervention, mandate), plus cross-cutting items X1 to X5.</t>
+          <t>One row per transition (T1 to T6), per continuum (Officer, Soldier), per fact (promotion point, development intervention, mandate), plus cross-cutting items X1 to X8.</t>
         </is>
       </c>
     </row>
@@ -2816,62 +2981,76 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>KNOWN: confirmed against an authoritative source.</t>
+          <t>STATED 9 SEP: stated at the NZALC meeting of 9 Sep 2026 (Mike and Dave). Treated as the working position; still to be checked against promotion policy or the course data sheet named in the row.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
+          <t>KNOWN: confirmed against an authoritative source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
           <t>NOT APPLICABLE: the category does not apply to this transition for this continuum (state why in Notes).</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr"/>
-    </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>CATEGORY MEANINGS</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Promotion point: Which Army promotion or career point corresponds to this LDF transition?</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>Development intervention: Which course or programme develops the individual for this transition (SOLO code, LDS, ELDA, promotion course)?</t>
+          <t>Promotion point: Which Army promotion or career point corresponds to this LDF transition?</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
+          <t>Development intervention: Which course or programme develops the individual for this transition (SOLO code, LDS, ELDA, promotion course)?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
           <t>Mandate: Is that development a prerequisite for promotion, embedded in the promotion course, expected but not mandatory, or unconnected?</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr"/>
-    </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>PRIORITY</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>The Officer Mandate rows at T2 and T3 decide the piece. Populate those first.</t>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>The Officer Mandate rows at T2 to T4 decide the piece: confirm the meeting's statements against promotion policy (X1) first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Then the Soldier Mandate row at T3 (Dave: is ILD LDS Lead Systems a prerequisite in the WO promotion-course CDS?).</t>
         </is>
       </c>
     </row>

--- a/output/ldf-alignment-data-required.xlsx
+++ b/output/ldf-alignment-data-required.xlsx
@@ -56,7 +56,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -76,6 +76,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFBEA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CDD2B7"/>
       </patternFill>
     </fill>
     <fill>
@@ -110,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -125,6 +130,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -641,7 +649,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>T1-O-DEVE</t>
+          <t>T1-O-DEV</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -696,7 +704,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>T1-O-MAND</t>
+          <t>T1-O-LINK</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -721,12 +729,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Career linkage</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Is that development a prerequisite for promotion, embedded in the promotion course, expected but not mandatory, or unconnected?</t>
+          <t>Where does the link between the development and the transition sit: 4 formally mandated (in policy or embedded in the qualifying course), 3 functionally required (policed, not in policy), 2 expected (self-selected, high uptake), 1 self-selected (uptake by inclination), 0 unconnected?</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -736,7 +744,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Meeting 9 Sep: Embedded: qualifying on NZCC qualifies both LDS and ELDA Lead Teams.</t>
+          <t>Meeting 9 Sep: Level 4, formally mandated: embedded in NZCC; qualifying on NZCC qualifies both LDS and ELDA Lead Teams.</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -806,7 +814,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>T1-R-DEVE</t>
+          <t>T1-R-DEV</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -861,7 +869,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>T1-R-MAND</t>
+          <t>T1-R-LINK</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -886,12 +894,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Career linkage</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Is that development a prerequisite for promotion, embedded in the promotion course, expected but not mandatory, or unconnected?</t>
+          <t>Where does the link between the development and the transition sit: 4 formally mandated (in policy or embedded in the qualifying course), 3 functionally required (policed, not in policy), 2 expected (self-selected, high uptake), 1 self-selected (uptake by inclination), 0 unconnected?</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -901,7 +909,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Meeting 9 Sep: Mandated for PTE to LCPL as an included course within the JNCO course.</t>
+          <t>Meeting 9 Sep: Level 4, formally mandated: an included course within the JNCO course for PTE to LCPL.</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -971,7 +979,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>T2-O-DEVE</t>
+          <t>T2-O-DEV</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1026,7 +1034,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>T2-O-MAND</t>
+          <t>T2-O-LINK</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1051,12 +1059,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Career linkage</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Is that development a prerequisite for promotion, embedded in the promotion course, expected but not mandatory, or unconnected?</t>
+          <t>Where does the link between the development and the transition sit: 4 formally mandated (in policy or embedded in the qualifying course), 3 functionally required (policed, not in policy), 2 expected (self-selected, high uptake), 1 self-selected (uptake by inclination), 0 unconnected?</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1066,12 +1074,12 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Meeting 9 Sep: Recommended, not mandated in promotion policy. Policed in function by OCS and COs: no 2LT or LT promotes to CAPT without it in practice. The single most important cell: confirm against promotion policy.</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>STATED 9 SEP</t>
+          <t>Meeting 9 Sep: Level 3, functionally required: not in promotion policy, but policed by OCS and COs so that no 2LT or LT promotes to CAPT without it in practice. The single most important cell: confirm the policy position.</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>TO CONFIRM</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr"/>
@@ -1136,7 +1144,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>T2-R-DEVE</t>
+          <t>T2-R-DEV</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1191,7 +1199,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>T2-R-MAND</t>
+          <t>T2-R-LINK</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1216,12 +1224,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Career linkage</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Is that development a prerequisite for promotion, embedded in the promotion course, expected but not mandatory, or unconnected?</t>
+          <t>Where does the link between the development and the transition sit: 4 formally mandated (in policy or embedded in the qualifying course), 3 functionally required (policed, not in policy), 2 expected (self-selected, high uptake), 1 self-selected (uptake by inclination), 0 unconnected?</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1231,7 +1239,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Meeting 9 Sep: Mandated in promotion policy: CPL promoting to SGT must complete the SNCO course, which carries it. 'Very clear on the NCO front.'</t>
+          <t>Meeting 9 Sep: Level 4, formally mandated in promotion policy: CPL promoting to SGT must complete the SNCO course, which carries it. 'Very clear on the NCO front.'</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1301,7 +1309,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>T3-O-DEVE</t>
+          <t>T3-O-DEV</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1356,7 +1364,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>T3-O-MAND</t>
+          <t>T3-O-LINK</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1381,12 +1389,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Career linkage</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Is that development a prerequisite for promotion, embedded in the promotion course, expected but not mandatory, or unconnected?</t>
+          <t>Where does the link between the development and the transition sit: 4 formally mandated (in policy or embedded in the qualifying course), 3 functionally required (policed, not in policy), 2 expected (self-selected, high uptake), 1 self-selected (uptake by inclination), 0 unconnected?</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1396,7 +1404,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Meeting 9 Sep: Neither ELDA Lead Systems nor ILD LDS Lead Systems is mandated; neither is policed in function; uptake self-selecting. Confirm against promotion policy.</t>
+          <t>Meeting 9 Sep: Level 1, self-selected: neither ELDA Lead Systems nor ILD LDS Lead Systems is mandated or policed; uptake rests on inclination. The weakest point on either continuum.</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1466,7 +1474,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>T3-R-DEVE</t>
+          <t>T3-R-DEV</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1521,7 +1529,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>T3-R-MAND</t>
+          <t>T3-R-LINK</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1546,12 +1554,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Career linkage</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Is that development a prerequisite for promotion, embedded in the promotion course, expected but not mandatory, or unconnected?</t>
+          <t>Where does the link between the development and the transition sit: 4 formally mandated (in policy or embedded in the qualifying course), 3 functionally required (policed, not in policy), 2 expected (self-selected, high uptake), 1 self-selected (uptake by inclination), 0 unconnected?</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1561,12 +1569,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Meeting 9 Sep: ELDA Lead Systems mandated on the WO course. Whether ILD LDS Lead Systems is a prerequisite for WO2: understanding is yes, with a question mark. Dave to check the promotion-course CDS.</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>STATED 9 SEP</t>
+          <t>Meeting 9 Sep: Level 4 for ELDA Lead Systems (mandated on the WO course). ILD LDS Lead Systems as a WO2 prerequisite: 'understanding is yes', with a question mark. Dave to check the promotion-course CDS.</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>TO CONFIRM</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr"/>
@@ -1631,7 +1639,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>T4-O-DEVE</t>
+          <t>T4-O-DEV</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1686,7 +1694,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>T4-O-MAND</t>
+          <t>T4-O-LINK</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1711,12 +1719,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Career linkage</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Is that development a prerequisite for promotion, embedded in the promotion course, expected but not mandatory, or unconnected?</t>
+          <t>Where does the link between the development and the transition sit: 4 formally mandated (in policy or embedded in the qualifying course), 3 functionally required (policed, not in policy), 2 expected (self-selected, high uptake), 1 self-selected (uptake by inclination), 0 unconnected?</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1726,12 +1734,12 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Meeting 9 Sep: Not mandated; impression is that all MAJ to LTCOL complete it. Confirm against promotion policy.</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>STATED 9 SEP</t>
+          <t>Meeting 9 Sep: Level 2, expected: not mandated; impression is that all MAJ to LTCOL complete it. Confirm against promotion policy.</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>TO CONFIRM</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr"/>
@@ -1796,7 +1804,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>T4-R-DEVE</t>
+          <t>T4-R-DEV</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1851,7 +1859,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>T4-R-MAND</t>
+          <t>T4-R-LINK</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1876,12 +1884,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Career linkage</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Is that development a prerequisite for promotion, embedded in the promotion course, expected but not mandatory, or unconnected?</t>
+          <t>Where does the link between the development and the transition sit: 4 formally mandated (in policy or embedded in the qualifying course), 3 functionally required (policed, not in policy), 2 expected (self-selected, high uptake), 1 self-selected (uptake by inclination), 0 unconnected?</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1891,12 +1899,12 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Meeting 9 Sep: Expected for promotion to WO1; 'pretty sure' not mandated in policy; most attend subject to an ILD seat. Confirm against promotion policy.</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>STATED 9 SEP</t>
+          <t>Meeting 9 Sep: Level 2, expected: expected for promotion to WO1; 'pretty sure' not in policy; most attend subject to an ILD seat. Confirm against promotion policy.</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>TO CONFIRM</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr"/>
@@ -1961,7 +1969,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>T5-O-DEVE</t>
+          <t>T5-O-DEV</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -2016,7 +2024,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>T5-O-MAND</t>
+          <t>T5-O-LINK</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -2041,12 +2049,12 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Career linkage</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Is that development a prerequisite for promotion, embedded in the promotion course, expected but not mandatory, or unconnected?</t>
+          <t>Where does the link between the development and the transition sit: 4 formally mandated (in policy or embedded in the qualifying course), 3 functionally required (policed, not in policy), 2 expected (self-selected, high uptake), 1 self-selected (uptake by inclination), 0 unconnected?</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2056,7 +2064,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Meeting 9 Sep: Mandate not stated; attendance without exception (selected, scrutinised, ambitious).</t>
+          <t>Meeting 9 Sep: Level 2, expected: ILD pathway; attendance without exception (selected, scrutinised, ambitious). Mandate not stated.</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -2126,7 +2134,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>T5-R-DEVE</t>
+          <t>T5-R-DEV</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -2181,7 +2189,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>T5-R-MAND</t>
+          <t>T5-R-LINK</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -2206,12 +2214,12 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Career linkage</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Is that development a prerequisite for promotion, embedded in the promotion course, expected but not mandatory, or unconnected?</t>
+          <t>Where does the link between the development and the transition sit: 4 formally mandated (in policy or embedded in the qualifying course), 3 functionally required (policed, not in policy), 2 expected (self-selected, high uptake), 1 self-selected (uptake by inclination), 0 unconnected?</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2221,7 +2229,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Meeting 9 Sep: Mandate not stated; attendance without exception.</t>
+          <t>Meeting 9 Sep: Level 2, expected: ILD pathway; attendance without exception. Mandate not stated.</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -2291,7 +2299,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>T6-O-DEVE</t>
+          <t>T6-O-DEV</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -2346,7 +2354,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>T6-O-MAND</t>
+          <t>T6-O-LINK</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -2371,12 +2379,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Career linkage</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Is that development a prerequisite for promotion, embedded in the promotion course, expected but not mandatory, or unconnected?</t>
+          <t>Where does the link between the development and the transition sit: 4 formally mandated (in policy or embedded in the qualifying course), 3 functionally required (policed, not in policy), 2 expected (self-selected, high uptake), 1 self-selected (uptake by inclination), 0 unconnected?</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2386,7 +2394,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Meeting 9 Sep: Mandate not stated; all complete it well before required.</t>
+          <t>Meeting 9 Sep: Level 2, expected: senior selection pathway; all complete it well before required. Mandate not stated.</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -2456,7 +2464,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>T6-R-DEVE</t>
+          <t>T6-R-DEV</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2511,7 +2519,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>T6-R-MAND</t>
+          <t>T6-R-LINK</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2536,12 +2544,12 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Career linkage</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Is that development a prerequisite for promotion, embedded in the promotion course, expected but not mandatory, or unconnected?</t>
+          <t>Where does the link between the development and the transition sit: 4 formally mandated (in policy or embedded in the qualifying course), 3 functionally required (policed, not in policy), 2 expected (self-selected, high uptake), 1 self-selected (uptake by inclination), 0 unconnected?</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2551,7 +2559,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Meeting 9 Sep: Mandate not stated; all complete it well before required.</t>
+          <t>Meeting 9 Sep: Level 2, expected: senior selection pathway; all complete it well before required. Mandate not stated.</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
@@ -2597,7 +2605,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="5" t="inlineStr">
+      <c r="J38" s="6" t="inlineStr">
         <is>
           <t>DATA REQUIRED</t>
         </is>
@@ -2640,7 +2648,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="5" t="inlineStr">
+      <c r="J39" s="6" t="inlineStr">
         <is>
           <t>DATA REQUIRED</t>
         </is>
@@ -2683,7 +2691,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="5" t="inlineStr">
+      <c r="J40" s="6" t="inlineStr">
         <is>
           <t>DATA REQUIRED</t>
         </is>
@@ -2769,7 +2777,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="5" t="inlineStr">
+      <c r="J42" s="6" t="inlineStr">
         <is>
           <t>DATA REQUIRED</t>
         </is>
@@ -2924,133 +2932,157 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>LDF ALIGNMENT: DATA REQUIRED REGISTER</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr"/>
+      <c r="A2" s="8" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>One row per transition (T1 to T6), per continuum (Officer, Soldier), per fact (promotion point, development intervention, mandate), plus cross-cutting items X1 to X8.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>Populate the three cream columns: Answer, Source cited, Notes. Set Status when done.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr"/>
+      <c r="A5" s="8" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>STATUS VALUES</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>DATA REQUIRED: nothing in hand.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>TO CONFIRM: something in hand but from an estimate (the Leadership Levels poster) or a session document, not authoritative policy.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>STATED 9 SEP: stated at the NZALC meeting of 9 Sep 2026 (Mike and Dave). Treated as the working position; still to be checked against promotion policy or the course data sheet named in the row.</t>
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>STATED 9 SEP: stated at the NZALC meeting of 9 Sep 2026 (Mike and Dave); the transcript governs over the generated notes. Treated as the working position; still to be checked against an authoritative source.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>TO CONFIRM also marks the career-linkage cells where the meeting itself left a question mark or where a policy check decides the state (officer T2 to T4, soldier T3 and T4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>KNOWN: confirmed against an authoritative source.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>NOT APPLICABLE: the category does not apply to this transition for this continuum (state why in Notes).</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr"/>
-    </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>CATEGORY MEANINGS</t>
-        </is>
-      </c>
+      <c r="A13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
+          <t>CATEGORY MEANINGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
           <t>Promotion point: Which Army promotion or career point corresponds to this LDF transition?</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>Development intervention: Which course or programme develops the individual for this transition (SOLO code, LDS, ELDA, promotion course)?</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Mandate: Is that development a prerequisite for promotion, embedded in the promotion course, expected but not mandatory, or unconnected?</t>
-        </is>
-      </c>
-    </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr"/>
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>Career linkage: Where does the link between the development and the transition sit: 4 formally mandated (in policy or embedded in the qualifying course), 3 functionally required (policed, not in policy), 2 expected (self-selected, high uptake), 1 self-selected (uptake by inclination), 0 unconnected?</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>PRIORITY</t>
-        </is>
-      </c>
+      <c r="A18" s="8" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>The Officer Mandate rows at T2 to T4 decide the piece: confirm the meeting's statements against promotion policy (X1) first.</t>
+          <t>PRIORITY</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>Then the Soldier Mandate row at T3 (Dave: is ILD LDS Lead Systems a prerequisite in the WO promotion-course CDS?).</t>
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>The Officer Career linkage rows at T2 to T4 decide the piece: confirm the meeting's statements against promotion policy (X1) first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Then the Soldier Career linkage row at T3 (Dave: is ILD LDS Lead Systems a prerequisite in the WO promotion-course CDS?).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>LINKAGE SCALE</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>4 formally mandated; 3 functionally required; 2 expected (high uptake); 1 self-selected (uptake by inclination); 0 unconnected. Record the level in the Answer column once confirmed.</t>
         </is>
       </c>
     </row>
